--- a/PCB_Project/Project Outputs for uz_per_torque_kistler_burster/Rev1/BOM_JLC/BOM_JLC_uz_per_torque_kistler_burster_Rev1.xlsx
+++ b/PCB_Project/Project Outputs for uz_per_torque_kistler_burster/Rev1/BOM_JLC/BOM_JLC_uz_per_torque_kistler_burster_Rev1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nina Diringer\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DE8EB2E-1444-43AC-B493-6D6FAFC4EBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{562921D8-9B38-45C5-8AAE-94F440E3A08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25005" yWindow="3915" windowWidth="17280" windowHeight="8970" xr2:uid="{DEDBC440-075A-406D-86D6-B716162FFC2F}"/>
+    <workbookView xWindow="-28020" yWindow="870" windowWidth="21600" windowHeight="11325" xr2:uid="{AD2431E3-B3BD-4A1F-9E25-FA4AAEA00534}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC_uz_per_torque_kistler_b" sheetId="1" r:id="rId1"/>
@@ -561,7 +561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE278DF-CCBC-4E9E-9289-F2CE24EE8BA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297EA7CC-3A3C-45A1-B682-3A53F520B8F7}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
